--- a/templates/office/EMP_ANL_050_연계규격협의서.xlsx
+++ b/templates/office/EMP_ANL_050_연계규격협의서.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 AI 기반 화장품 표시광고 심의 및 리스크 예방 시스템 구축</t>
+          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>(주)아모레퍼시픽 (HANBIT GLOBAL)</t>
+          <t>㈜한빛글로벌 (Hanbit Global Corp.)</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>㈜그로브소프트 (EMPASY)</t>
+          <t>㈜엠파시 (Empasy Inc.)</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 IT인프라팀, 화장품 RA Lab, R&amp;I ProductLab팀, MarketingHub 운영팀 (KT레몬 Option 검토)</t>
+          <t>한빛글로벌 IT인프라팀, 화장품 RA Lab, R&amp;I ProductLab팀, MarketingHub 운영팀 (KT레몬 Option 검토)</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>MarketingHub (티움넷)</t>
+          <t>MarketingHub (마케팅허브)</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 통합 SSO</t>
+          <t>한빛글로벌 통합 SSO</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>사내 임직원(HB-SSO) 통합 인증, 티움넷 뷰어 SSO 연동 및 권한 토큰 발급</t>
+          <t>사내 임직원(HB-SSO) 통합 인증, 마케팅허브 뷰어 SSO 연동 및 권한 토큰 발급</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>티움넷 심의 의뢰 메타데이터 접수 (300MB 원본은 FO 직접 업로드)</t>
+          <t>마케팅허브 심의 의뢰 메타데이터 접수 (300MB 원본은 FO 직접 업로드)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">

--- a/templates/office/EMP_ANL_050_연계규격협의서.xlsx
+++ b/templates/office/EMP_ANL_050_연계규격협의서.xlsx
@@ -526,7 +526,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 외부·내부 인터페이스 연계 규격 및 프로토콜 합의서</t>
+          <t>SyncFlow AI 시스템 외부·내부 인터페이스 연계 규격 및 프로토콜 합의서</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
+          <t>한빛글로벌 지능형 공급망 구매·조달 계약 및 부품 품질규격 AI 검증 플랫폼(SyncFlow AI) 구축</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>한빛글로벌 IT인프라팀, 화장품 RA Lab, R&amp;I ProductLab팀, MarketingHub 운영팀 (KT레몬 Option 검토)</t>
+          <t>한빛글로벌 IT인프라팀, 품질법무검증팀, 선행연구소 PLM-Nexus팀, SRM-Portal 운영팀 (HB-Monitor Option 검토)</t>
         </is>
       </c>
     </row>
@@ -700,22 +700,22 @@
     <row r="5">
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>SYS-MKTHUB</t>
+          <t>SYS-SRMP</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>MarketingHub (마케팅허브)</t>
+          <t>SRM-Portal (전자구매포털)</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>경영지원 / 마케팅심의포털</t>
+          <t>경영지원 / 구매조달검증포털</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>광고 시안·동영상 심의 의뢰 접수, 대조 뷰어 연동 및 최종 승인/반려 결과 회신</t>
+          <t>구매계약 계약·도서·설계도면 검증 요청 접수, 대조 뷰어 연동 및 최종 승인/반려 결과 회신</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>심의의뢰번호, 브랜드/제품코드, 시안파일, 판정등급, 뷰어링크, 의견서 PDF</t>
+          <t>검증요청번호, 사업본부/제품코드, 계약·도서파일, 판정등급, 뷰어링크, 의견서 PDF</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -737,22 +737,22 @@
     <row r="6">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>SYS-PRODLAB</t>
+          <t>SYS-PLMNEXUS</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>ProductLab &amp; 전성분 RDB</t>
+          <t>PLM-Nexus &amp; 자재BOM RDB</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>R&amp;I 기술원 / 연구전략Lab</t>
+          <t>선행연구소 기술원 / 공급망혁신팀</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>제품 처방·전성분 배합한도 조회 및 인체적용시험·효능 실증 보고서 연동</t>
+          <t>제품 설계사양·자재BOM 유해물질한도 조회 및 공인신뢰성시험·성능규격 시험검증 보고서 연동</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>제품/처방코드, 성분명(INCI), 배합한도(%), 시험성적서 메타 및 실증문구</t>
+          <t>제품/설계사양코드, 성분명(CAS/RoHS), 유해물질한도(%), 시험성적서 메타 및 시험검증조항</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>사내 임직원(HB-SSO) 통합 인증, 마케팅허브 뷰어 SSO 연동 및 권한 토큰 발급</t>
+          <t>사내 임직원(HB-SSO) 통합 인증, 전자구매포털 뷰어 SSO 연동 및 권한 토큰 발급</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>사번, 성명, 부서코드, 역할권한(BM/RA/연구원/관리자), JWT 토큰</t>
+          <t>사번, 성명, 부서코드, 역할권한(BM/QA/연구원/관리자), JWT 토큰</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>광고 시안 원본, 동영상 사용자 지정 캡처 장면(스냅샷), 심의 리포트 PDF 보관</t>
+          <t>구매계약 계약·도서 원본, 설계도면 사용자 지정 도면 스냅샷(스냅샷), 검증 리포트 PDF 보관</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>PPTX, PDF, 상세페이지 JPG, MP4 영상, 캡처 스냅샷 이미지, 리포트 PDF</t>
+          <t>PPTX, PDF, 기술시방서 JPG, CAD 설계도면, 스냅샷 스냅샷 이미지, 리포트 PDF</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>[Option] KT 레몬 (Lemon)</t>
+          <t>[Option] HB-Monitor (Lemon)</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>R&amp;I 화장품 연구소</t>
+          <t>선행연구소 전장부품 연구소</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -973,22 +973,22 @@
     <row r="5">
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>IF-MKTH-001</t>
+          <t>IF-SRM-001</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>마케팅허브 심의 의뢰 메타데이터 접수 (300MB 원본은 FO 직접 업로드)</t>
+          <t>전자구매포털 검증 요청 메타데이터 접수 (300MB 원본은 FO 직접 업로드)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>MarketingHub</t>
+          <t>SRM-Portal</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>SyncGuard AI (FO API :18085)</t>
+          <t>SyncFlow AI (FO API :18085)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="6">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>IF-MKTH-002</t>
+          <t>IF-SRM-002</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>AI 심의 대조 뷰어 링크 및 최종 결과 회신</t>
+          <t>AI 검증 대조 뷰어 링크 및 최종 결과 회신</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SyncGuard AI (FO API :18085)</t>
+          <t>SyncFlow AI (FO API :18085)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>MarketingHub</t>
+          <t>SRM-Portal</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -1082,22 +1082,22 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>제품 전성분·원료 배합한도 규격 조회</t>
+          <t>제품 자재BOM·원소재 유해물질한도 규격 조회</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>ProductLab/전성분DB</t>
+          <t>PLM-Nexus/자재BOMDB</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>수시 (심의시) / Sync</t>
+          <t>수시 (검증시) / Sync</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>인체적용시험·효능 실증 보고서 연동</t>
+          <t>공인신뢰성시험·성능규격 시험검증 보고서 연동</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>ProductLab</t>
+          <t>PLM-Nexus</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>SyncGuard AI (Batch :18084)</t>
+          <t>SyncFlow AI (Batch :18084)</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>대용량 시안·동영상(300MB) 및 캡처 장면 S3 직접 업로드</t>
+          <t>대용량 계약·도서·설계도면(300MB) 및 도면 스냅샷 S3 직접 업로드</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1342,22 +1342,22 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>[Option] KT 레몬 연구보고서 벡터 검색</t>
+          <t>[Option] HB-Monitor 연구보고서 벡터 검색</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>KT 레몬</t>
+          <t>HB-Monitor</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>수시 (심의시) / Option</t>
+          <t>수시 (검증시) / Option</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>수행사 / MarketingHub</t>
+          <t>수행사 / SRM-Portal</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>SyncGuard AI 운영팀</t>
+          <t>SyncFlow AI 운영팀</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
